--- a/files/九龙-启德-Monaco Marine.xlsx
+++ b/files/九龙-启德-Monaco Marine.xlsx
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>20986000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>29433</v>
+        <v>29392</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>20986000</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>29433</v>
+        <v>29392</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3621,14 +3621,14 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
         <v>8939000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>27253</v>
+        <v>27336</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>8939000</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>27253</v>
+        <v>27336</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -35608,9 +35608,9 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>A | 713呎 (3房)
+          <t>A | 714呎 (3房)
 $2099万
-$29,433/呎
+$29,392/呎
 (22年-05月-19日)</t>
         </is>
       </c>
@@ -36019,10 +36019,10 @@
       </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
-          <t>H | 328呎 (1房)
+          <t>H | 327呎 (1房)
 $894万
-$27,253/呎
-(26年-07月-06日)</t>
+$27,336/呎
+(26年-07月-31日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-Monaco Marine.xlsx
+++ b/files/九龙-启德-Monaco Marine.xlsx
@@ -15020,7 +15020,7 @@
         </is>
       </c>
       <c r="E233" s="4" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
@@ -15029,14 +15029,14 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
         <v>8577000</v>
       </c>
       <c r="I233" s="5" t="n">
-        <v>26149</v>
+        <v>26229</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>8577000</v>
       </c>
       <c r="L233" s="5" t="n">
-        <v>26149</v>
+        <v>26229</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
@@ -37645,10 +37645,10 @@
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
-          <t>H | 328呎 (1房)
+          <t>H | 327呎 (1房)
 $858万
-$26,149/呎
-(26年-07月-18日)</t>
+$26,229/呎
+(26年-08月-10日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-Monaco Marine.xlsx
+++ b/files/九龙-启德-Monaco Marine.xlsx
@@ -26676,7 +26676,7 @@
         </is>
       </c>
       <c r="E421" s="4" t="n">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F421" s="3" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>14001000</v>
       </c>
       <c r="I421" s="5" t="n">
-        <v>26669</v>
+        <v>26719</v>
       </c>
       <c r="J421" s="3" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>14001000</v>
       </c>
       <c r="L421" s="5" t="n">
-        <v>26669</v>
+        <v>26719</v>
       </c>
       <c r="M421" s="3" t="inlineStr">
         <is>
@@ -39391,9 +39391,9 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>A | 525呎 (2房)
+          <t>A | 524呎 (2房)
 $1400万
-$26,669/呎
+$26,719/呎
 (22年-05月-16日)</t>
         </is>
       </c>

--- a/files/九龙-启德-Monaco Marine.xlsx
+++ b/files/九龙-启德-Monaco Marine.xlsx
@@ -764,34 +764,34 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
-        <v>9886000</v>
+        <v>8799000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>30140</v>
+        <v>26826</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>8798540</v>
+        <v>8799000</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>26825</v>
+        <v>26826</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -35472,7 +35472,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -35482,7 +35482,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -35591,12 +35591,12 @@
 (22年-06月-01日)</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>H | 328呎 (1房)
-$989万
-$30,140/呎
-(在售)</t>
+$880万
+$26,826/呎
+(26年-09月-02日)</t>
         </is>
       </c>
     </row>
